--- a/contest_registration_forms/048_gaming_tournament_registration_form--contest_registration_forms.xlsx
+++ b/contest_registration_forms/048_gaming_tournament_registration_form--contest_registration_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -761,8 +761,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="25" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="19" customWidth="1" min="2" max="2"/>
+    <col width="19" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -790,12 +790,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'name':_'player_1',_'label':_'player_1'}</t>
+          <t>player_1</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'name': 'player_1', 'label': 'Player 1'}</t>
+          <t>Player 1</t>
         </is>
       </c>
     </row>
@@ -807,12 +807,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'name':_'player_2',_'label':_'player_2'}</t>
+          <t>player_2</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'name': 'player_2', 'label': 'Player 2'}</t>
+          <t>Player 2</t>
         </is>
       </c>
     </row>
@@ -824,12 +824,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'name':_'player_3',_'label':_'player_3'}</t>
+          <t>player_3</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'name': 'player_3', 'label': 'Player 3'}</t>
+          <t>Player 3</t>
         </is>
       </c>
     </row>
@@ -841,12 +841,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'name':_'player_4',_'label':_'player_4'}</t>
+          <t>player_4</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'name': 'player_4', 'label': 'Player 4'}</t>
+          <t>Player 4</t>
         </is>
       </c>
     </row>
@@ -858,12 +858,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'name':_'player_5',_'label':_'player_5'}</t>
+          <t>player_5</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'name': 'player_5', 'label': 'Player 5'}</t>
+          <t>Player 5</t>
         </is>
       </c>
     </row>
@@ -875,12 +875,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'name':_'player_6',_'label':_'player_6'}</t>
+          <t>player_6</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'name': 'player_6', 'label': 'Player 6'}</t>
+          <t>Player 6</t>
         </is>
       </c>
     </row>
@@ -892,12 +892,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'name':_'player_7',_'label':_'player_7'}</t>
+          <t>player_7</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'name': 'player_7', 'label': 'Player 7'}</t>
+          <t>Player 7</t>
         </is>
       </c>
     </row>
@@ -909,12 +909,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'name':_'player_8',_'label':_'player_8'}</t>
+          <t>player_8</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'name': 'player_8', 'label': 'Player 8'}</t>
+          <t>Player 8</t>
         </is>
       </c>
     </row>
@@ -926,12 +926,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'name':_'discord_username',_'label':_'discord_username'}</t>
+          <t>discord_username</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'name': 'discord_username', 'label': 'Discord Username'}</t>
+          <t>Discord Username</t>
         </is>
       </c>
     </row>
@@ -943,12 +943,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'name':_'discord_tag',_'label':_'discord_tag'}</t>
+          <t>discord_tag</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'name': 'discord_tag', 'label': 'Discord Tag'}</t>
+          <t>Discord Tag</t>
         </is>
       </c>
     </row>
@@ -960,12 +960,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'name':_'discord_channel',_'label':_'discord_channel'}</t>
+          <t>discord_channel</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'name': 'discord_channel', 'label': 'Discord Channel'}</t>
+          <t>Discord Channel</t>
         </is>
       </c>
     </row>
@@ -977,12 +977,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'name':_'discord_server',_'label':_'discord_server'}</t>
+          <t>discord_server</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'name': 'discord_server', 'label': 'Discord Server'}</t>
+          <t>Discord Server</t>
         </is>
       </c>
     </row>
@@ -994,12 +994,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'name':_'game_1',_'label':_'game_1'}</t>
+          <t>game_1</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'name': 'game_1', 'label': 'Game 1'}</t>
+          <t>Game 1</t>
         </is>
       </c>
     </row>
@@ -1011,12 +1011,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'name':_'game_2',_'label':_'game_2'}</t>
+          <t>game_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'name': 'game_2', 'label': 'Game 2'}</t>
+          <t>Game 2</t>
         </is>
       </c>
     </row>
@@ -1028,12 +1028,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'name':_'game_3',_'label':_'game_3'}</t>
+          <t>game_3</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'name': 'game_3', 'label': 'Game 3'}</t>
+          <t>Game 3</t>
         </is>
       </c>
     </row>
@@ -1045,12 +1045,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'name':_'game_4',_'label':_'game_4'}</t>
+          <t>game_4</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'name': 'game_4', 'label': 'Game 4'}</t>
+          <t>Game 4</t>
         </is>
       </c>
     </row>
@@ -1062,12 +1062,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'name':_'game_5',_'label':_'game_5'}</t>
+          <t>game_5</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'name': 'game_5', 'label': 'Game 5'}</t>
+          <t>Game 5</t>
         </is>
       </c>
     </row>
@@ -1079,12 +1079,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'name':_'tournament_type_1',_'label':_'tournament_type_1'}</t>
+          <t>tournament_type_1</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'name': 'tournament_type_1', 'label': 'Tournament Type 1'}</t>
+          <t>Tournament Type 1</t>
         </is>
       </c>
     </row>
@@ -1096,12 +1096,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'name':_'tournament_type_2',_'label':_'tournament_type_2'}</t>
+          <t>tournament_type_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'name': 'tournament_type_2', 'label': 'Tournament Type 2'}</t>
+          <t>Tournament Type 2</t>
         </is>
       </c>
     </row>
@@ -1113,12 +1113,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'name':_'tournament_type_3',_'label':_'tournament_type_3'}</t>
+          <t>tournament_type_3</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'name': 'tournament_type_3', 'label': 'Tournament Type 3'}</t>
+          <t>Tournament Type 3</t>
         </is>
       </c>
     </row>
@@ -1130,12 +1130,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'name':_'division_1',_'label':_'division_1'}</t>
+          <t>division_1</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'name': 'division_1', 'label': 'Division 1'}</t>
+          <t>Division 1</t>
         </is>
       </c>
     </row>
@@ -1147,12 +1147,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'name':_'division_2',_'label':_'division_2'}</t>
+          <t>division_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'name': 'division_2', 'label': 'Division 2'}</t>
+          <t>Division 2</t>
         </is>
       </c>
     </row>
@@ -1164,12 +1164,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'name':_'division_3',_'label':_'division_3'}</t>
+          <t>division_3</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'name': 'division_3', 'label': 'Division 3'}</t>
+          <t>Division 3</t>
         </is>
       </c>
     </row>
@@ -1181,12 +1181,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'name':_'division_4',_'label':_'division_4'}</t>
+          <t>division_4</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'name': 'division_4', 'label': 'Division 4'}</t>
+          <t>Division 4</t>
         </is>
       </c>
     </row>
